--- a/www/terminologies/ASS-X09-DepartementOM-RegionOM.xlsx
+++ b/www/terminologies/ASS-X09-DepartementOM-RegionOM.xlsx
@@ -99,13 +99,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_G09-DepartementOM/FHIR/TRE-G09-DepartementOM|20240628120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_G09-DepartementOM/FHIR/TRE-G09-DepartementOM</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R30-RegionOM/FHIR/TRE-R30-RegionOM|20240628120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R30-RegionOM/FHIR/TRE-R30-RegionOM</t>
   </si>
   <si>
     <t>01</t>
